--- a/Result/profitability/1615.xlsx
+++ b/Result/profitability/1615.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05625</v>
+        <v>1.1125</v>
       </c>
       <c r="N2" t="n">
-        <v>20.015</v>
+        <v>20.61125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.985</v>
+        <v>1.0625</v>
       </c>
       <c r="N3" t="n">
-        <v>18.85875</v>
+        <v>19.2825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88875</v>
+        <v>0.9550000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>17.18125</v>
+        <v>17.45625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.7675</v>
       </c>
       <c r="N5" t="n">
-        <v>14.58</v>
+        <v>14.705</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5487500000000001</v>
+        <v>0.6</v>
       </c>
       <c r="N6" t="n">
-        <v>12.08</v>
+        <v>12.04875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45625</v>
+        <v>0.4725</v>
       </c>
       <c r="N7" t="n">
-        <v>10.24625</v>
+        <v>9.98625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3350000000000001</v>
+        <v>0.4162500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.767500000000001</v>
+        <v>7.70125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.2987500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>6.350000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1611</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1242</v>
+      </c>
+      <c r="E75" t="n">
+        <v>368</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>301</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>78</v>
+      </c>
+      <c r="J75" t="n">
+        <v>379</v>
+      </c>
+      <c r="K75" t="n">
+        <v>312</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.8175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6914893617021278</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5300000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02263989747970963</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3032786885245902</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04570383912248621</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
